--- a/jira_export_2026-08-27.xlsx
+++ b/jira_export_2026-08-27.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>25,876 €</t>
+          <t>29,534 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -770,7 +770,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>12,149 €</t>
+          <t>15,807 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>423 h</t>
+          <t>425 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -903,7 +903,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>266</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1736,7 +1736,7 @@
         <v>2419</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>2419</v>
+        <v>3144.7</v>
       </c>
       <c r="P14" s="15" t="n">
         <v>0</v>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>394.75</v>
+        <v>789.5</v>
       </c>
       <c r="P16" s="15" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>726.25</v>
+        <v>1660</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
@@ -2952,7 +2952,7 @@
         <v>9623.1</v>
       </c>
       <c r="O31" s="16" t="n">
-        <v>0</v>
+        <v>1603.85</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
@@ -6660,7 +6660,7 @@
         <v>6</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>12.25</v>
+        <v>13.25</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>1504.3</v>
       </c>
       <c r="P83" s="12" t="n">
-        <v>122.8</v>
+        <v>113.53</v>
       </c>
     </row>
     <row r="84">
@@ -11438,10 +11438,10 @@
         <v>63800.79399999999</v>
       </c>
       <c r="O154" s="18" t="n">
-        <v>25875.837</v>
+        <v>29533.887</v>
       </c>
       <c r="P154" s="18" t="n">
-        <v>112.87</v>
+        <v>128.27</v>
       </c>
     </row>
   </sheetData>
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>169.5</v>
+        <v>170.5</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>32.25</v>
@@ -12308,7 +12308,7 @@
         <v>11.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>213.5</v>
+        <v>214.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>69.75</v>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
     </row>
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>116.5</v>
+        <v>117.5</v>
       </c>
     </row>
   </sheetData>
@@ -12445,13 +12445,13 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>371498</v>
+        <v>367840</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>137636</v>
+        <v>135582</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>233862</v>
+        <v>232258</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>147317</v>
@@ -12495,13 +12495,13 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>208143</v>
+        <v>204485</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>78831</v>
+        <v>76777</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>129312</v>
+        <v>127708</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>59957</v>
@@ -12524,13 +12524,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -12548,7 +12548,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 13 commande(s)</t>
+          <t>Épics créées ce mois — 14 commande(s)</t>
         </is>
       </c>
     </row>
@@ -13008,22 +13008,22 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35188</t>
+          <t>PDMDEP-35301</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35184</t>
+          <t>PDMDEP-35295</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -13043,32 +13043,32 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>00178947</t>
+          <t>00179371</t>
         </is>
       </c>
       <c r="I14" s="26" t="n">
-        <v>1736</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-35188</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178947</t>
         </is>
       </c>
       <c r="I15" s="25" t="n">
-        <v>1500</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -13133,83 +13133,107 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I16" s="26" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-34979</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34975</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>VILLE DE SURESNES</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>00178226</t>
+        </is>
+      </c>
+      <c r="I17" s="25" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I17" s="25" t="n">
+      <c r="I18" s="26" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="17" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>13 commande(s)</t>
-        </is>
-      </c>
-      <c r="I18" s="24" t="n">
-        <v>19898</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B19" s="17" t="n"/>
@@ -13220,17 +13244,17 @@
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>4 commande(s)</t>
+          <t>14 commande(s)</t>
         </is>
       </c>
       <c r="I19" s="24" t="n">
-        <v>7736</v>
+        <v>19898</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B20" s="17" t="n"/>
@@ -13241,10 +13265,31 @@
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="17" t="inlineStr">
         <is>
+          <t>5 commande(s)</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>7736</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="inlineStr">
+        <is>
           <t>9 commande(s)</t>
         </is>
       </c>
-      <c r="I20" s="24" t="n">
+      <c r="I21" s="24" t="n">
         <v>12162</v>
       </c>
     </row>

--- a/jira_export_2026-08-27.xlsx
+++ b/jira_export_2026-08-27.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>30,374 €</t>
+          <t>30,318 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>13,727 €</t>
+          <t>13,671 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>450 h</t>
+          <t>499 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L6" s="15" t="inlineStr"/>
       <c r="M6" s="15" t="inlineStr"/>
@@ -2393,10 +2393,10 @@
         <v>1892</v>
       </c>
       <c r="O23" s="17" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="P23" s="13" t="n">
-        <v>0</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="24">
@@ -4897,10 +4897,10 @@
         <v>625</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>945</v>
+        <v>652.5</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>112.84</v>
+        <v>77.91</v>
       </c>
     </row>
     <row r="59">
@@ -6829,10 +6829,10 @@
         <v>700</v>
       </c>
       <c r="O85" s="13" t="n">
-        <v>1504.3</v>
+        <v>1611.75</v>
       </c>
       <c r="P85" s="13" t="n">
-        <v>113.53</v>
+        <v>121.64</v>
       </c>
     </row>
     <row r="86">
@@ -10373,7 +10373,7 @@
         <v>20</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>20</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
@@ -11591,10 +11591,10 @@
         <v>63800.794</v>
       </c>
       <c r="O156" s="19" t="n">
-        <v>30373.887</v>
+        <v>30317.837</v>
       </c>
       <c r="P156" s="19" t="n">
-        <v>131.92</v>
+        <v>130.95</v>
       </c>
     </row>
   </sheetData>
@@ -12454,16 +12454,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>170.5</v>
+        <v>171</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>32.25</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>11.75</v>
+        <v>12.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>214.5</v>
+        <v>215.75</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>69.75</v>
@@ -12473,7 +12473,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12515,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>142.25</v>
+        <v>189.75</v>
       </c>
     </row>
   </sheetData>
@@ -12600,16 +12600,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>369300</v>
+        <v>369356</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>137042</v>
+        <v>137548</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>232258</v>
+        <v>231808</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>147317</v>
+        <v>146867</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21179</v>
@@ -12625,16 +12625,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>165655</v>
+        <v>165711</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>61105</v>
+        <v>61611</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>104551</v>
+        <v>104101</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>87360</v>
+        <v>86910</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>11307</v>

--- a/jira_export_2026-08-27.xlsx
+++ b/jira_export_2026-08-27.xlsx
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="L6" s="15" t="inlineStr"/>
       <c r="M6" s="15" t="inlineStr"/>
@@ -11594,7 +11594,7 @@
         <v>30317.837</v>
       </c>
       <c r="P156" s="19" t="n">
-        <v>130.95</v>
+        <v>130.81</v>
       </c>
     </row>
   </sheetData>
@@ -12460,10 +12460,10 @@
         <v>32.25</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>12.5</v>
+        <v>12.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>215.75</v>
+        <v>216</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>69.75</v>
@@ -12600,10 +12600,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>369356</v>
+        <v>369856</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>137548</v>
+        <v>138048</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>231808</v>
@@ -12625,10 +12625,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>165711</v>
+        <v>166211</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>61611</v>
+        <v>62111</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104101</v>
@@ -12679,7 +12679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12703,7 +12703,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 14 commande(s)</t>
+          <t>Épics créées ce mois — 15 commande(s)</t>
         </is>
       </c>
     </row>
@@ -12758,22 +12758,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35285</t>
+          <t>PDMDEP-35319</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35275</t>
+          <t>PDMDEP-35313</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TRETS</t>
+          <t>COMMUNE DE GAREOULT</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="F5" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>00179201</t>
+          <t>00179389</t>
         </is>
       </c>
       <c r="I5" s="26" t="n">
@@ -12803,22 +12803,22 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35212</t>
+          <t>PDMDEP-35285</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35275</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>COMMUNE DE TRETS</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00179038</t>
+          <t>00179201</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
@@ -12848,22 +12848,22 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35171</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35165</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LORGUES</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -12883,22 +12883,22 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00178865</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35156</t>
+          <t>PDMDEP-35171</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35148</t>
+          <t>PDMDEP-35165</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Les Portes En Ré</t>
+          <t>MAIRIE DE LORGUES</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -12928,32 +12928,32 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00178841</t>
+          <t>00178865</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
-        <v>250</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35156</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35148</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>Mairie de Les Portes En Ré</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -12973,22 +12973,22 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00178841</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>2035</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -13018,22 +13018,22 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>985</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35088</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35082</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>FREJUS</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -13063,32 +13063,32 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>00152501</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="I11" s="26" t="n">
-        <v>3541.5</v>
+        <v>985</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35008</t>
+          <t>PDMDEP-35088</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35000</t>
+          <t>PDMDEP-35082</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>10/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+          <t>FREJUS</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -13108,32 +13108,32 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>00178436</t>
+          <t>00152501</t>
         </is>
       </c>
       <c r="I12" s="27" t="n">
-        <v>500</v>
+        <v>3541.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-35008</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-35000</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>10/08/2026</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -13153,37 +13153,37 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178436</t>
         </is>
       </c>
       <c r="I13" s="26" t="n">
-        <v>4050</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35301</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-35295</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>27/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -13198,32 +13198,32 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>00179371</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="I14" s="27" t="n">
-        <v>2300</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35188</t>
+          <t>PDMDEP-35301</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-35184</t>
+          <t>PDMDEP-35295</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -13243,32 +13243,32 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>00178947</t>
+          <t>00179371</t>
         </is>
       </c>
       <c r="I15" s="26" t="n">
-        <v>1736</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34993</t>
+          <t>PDMDEP-35188</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34989</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>07/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Commune de Villeneuve D'Ascq</t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -13288,32 +13288,32 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>00178306</t>
+          <t>00178947</t>
         </is>
       </c>
       <c r="I16" s="27" t="n">
-        <v>1500</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-34993</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-34989</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -13333,83 +13333,107 @@
       </c>
       <c r="H17" s="15" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178306</t>
         </is>
       </c>
       <c r="I17" s="26" t="n">
-        <v>2200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>PDMDEP-34979</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34975</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>VILLE DE SURESNES</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>00178226</t>
+        </is>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
           <t>PDMDEP-34929</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-34925</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>04/08/2026</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>00178034</t>
         </is>
       </c>
-      <c r="I18" s="27" t="n">
+      <c r="I19" s="26" t="n">
         <v>2300</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="18" t="n"/>
-      <c r="D19" s="18" t="n"/>
-      <c r="E19" s="18" t="n"/>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="18" t="n"/>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>14 commande(s)</t>
-        </is>
-      </c>
-      <c r="I19" s="25" t="n">
-        <v>22198</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B20" s="18" t="n"/>
@@ -13420,17 +13444,17 @@
       <c r="G20" s="18" t="n"/>
       <c r="H20" s="18" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>15 commande(s)</t>
         </is>
       </c>
       <c r="I20" s="25" t="n">
-        <v>10036</v>
+        <v>22198</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B21" s="18" t="n"/>
@@ -13441,10 +13465,31 @@
       <c r="G21" s="18" t="n"/>
       <c r="H21" s="18" t="inlineStr">
         <is>
-          <t>9 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
+        <v>10036</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="18" t="inlineStr">
+        <is>
+          <t>10 commande(s)</t>
+        </is>
+      </c>
+      <c r="I22" s="25" t="n">
         <v>12162</v>
       </c>
     </row>

--- a/jira_export_2026-08-27.xlsx
+++ b/jira_export_2026-08-27.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>30,318 €</t>
+          <t>30,640 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>13,671 €</t>
+          <t>13,993 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>499 h</t>
+          <t>516 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P156"/>
+  <dimension ref="A1:P154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -961,7 +961,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>4.75</v>
+        <v>5.75</v>
       </c>
       <c r="L6" s="15" t="inlineStr"/>
       <c r="M6" s="15" t="inlineStr"/>
@@ -2390,9 +2390,9 @@
         </is>
       </c>
       <c r="N23" s="13" t="n">
-        <v>1892</v>
-      </c>
-      <c r="O23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="13" t="n">
         <v>129</v>
       </c>
       <c r="P23" s="13" t="n">
@@ -3873,7 +3873,7 @@
         <v>2</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>438.2</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>47.37</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="45">
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="N54" s="16" t="n">
-        <v>514.2</v>
+        <v>0</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>642.75</v>
@@ -5326,9 +5326,9 @@
         </is>
       </c>
       <c r="N64" s="16" t="n">
-        <v>400</v>
-      </c>
-      <c r="O64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="16" t="n">
@@ -5542,9 +5542,9 @@
         </is>
       </c>
       <c r="N67" s="13" t="n">
-        <v>1294.224</v>
-      </c>
-      <c r="O67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="13" t="n">
         <v>219.36</v>
       </c>
       <c r="P67" s="13" t="n">
@@ -6190,32 +6190,32 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -6225,69 +6225,69 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O77" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O77" s="13" t="n">
+        <v>109.972</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6297,69 +6297,69 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="16" t="n">
-        <v>109.972</v>
+        <v>285</v>
+      </c>
+      <c r="O78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>9.359999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
@@ -6385,16 +6385,16 @@
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>285</v>
+        <v>1325</v>
       </c>
       <c r="O79" s="17" t="n">
         <v>0</v>
@@ -6406,12 +6406,12 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
@@ -6457,16 +6457,16 @@
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>1325</v>
+        <v>120</v>
       </c>
       <c r="O80" s="17" t="n">
         <v>0</v>
@@ -6478,32 +6478,32 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
@@ -6529,16 +6529,16 @@
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>120</v>
+        <v>588</v>
       </c>
       <c r="O81" s="17" t="n">
         <v>0</v>
@@ -6550,27 +6550,27 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -6585,32 +6585,32 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K82" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>588</v>
+        <v>203.5</v>
       </c>
       <c r="O82" s="17" t="n">
         <v>0</v>
@@ -6622,12 +6622,12 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
@@ -6673,16 +6673,16 @@
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>203.5</v>
+        <v>300</v>
       </c>
       <c r="O83" s="17" t="n">
         <v>0</v>
@@ -6694,32 +6694,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6729,49 +6729,49 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="O84" s="17" t="n">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="O84" s="16" t="n">
+        <v>1934.1</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>0</v>
+        <v>126.83</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -6813,52 +6813,44 @@
         <v>6</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="L85" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-31546</t>
-        </is>
-      </c>
-      <c r="M85" s="12" t="inlineStr">
-        <is>
-          <t>00157816</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L85" s="12" t="inlineStr"/>
+      <c r="M85" s="12" t="inlineStr"/>
       <c r="N85" s="13" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="O85" s="13" t="n">
-        <v>1611.75</v>
+        <v>0</v>
       </c>
       <c r="P85" s="13" t="n">
-        <v>121.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6868,7 +6860,7 @@
       </c>
       <c r="G86" s="15" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H86" s="15" t="inlineStr">
@@ -6878,56 +6870,64 @@
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L86" s="15" t="inlineStr"/>
-      <c r="M86" s="15" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="L86" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-31468</t>
+        </is>
+      </c>
+      <c r="M86" s="15" t="inlineStr">
+        <is>
+          <t>00157346</t>
+        </is>
+      </c>
       <c r="N86" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="16" t="n">
-        <v>0</v>
+        <v>138.825</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>0</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
@@ -6937,49 +6937,49 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>416.475</v>
+        <v>210</v>
       </c>
       <c r="O87" s="17" t="n">
-        <v>138.825</v>
+        <v>0</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>19.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
@@ -7025,16 +7025,16 @@
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O88" s="17" t="n">
         <v>0</v>
@@ -7046,12 +7046,12 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
@@ -7097,16 +7097,16 @@
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>281</v>
+        <v>255</v>
       </c>
       <c r="O89" s="17" t="n">
         <v>0</v>
@@ -7118,12 +7118,12 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7158,29 +7158,29 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>130</v>
-      </c>
-      <c r="O90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="16" t="n">
@@ -7190,12 +7190,12 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7230,27 +7230,27 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>255</v>
+        <v>140</v>
       </c>
       <c r="O91" s="17" t="n">
         <v>0</v>
@@ -7262,32 +7262,32 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -7297,106 +7297,106 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>1.5</v>
+        <v>8.75</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="16" t="n">
-        <v>0</v>
+        <v>690</v>
+      </c>
+      <c r="O92" s="17" t="n">
+        <v>230</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>0</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
-        <v>140</v>
-      </c>
-      <c r="O93" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P93" s="13" t="n">
@@ -7406,27 +7406,27 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7446,44 +7446,44 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>8.75</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>690</v>
-      </c>
-      <c r="O94" s="17" t="n">
-        <v>230</v>
+        <v>0</v>
+      </c>
+      <c r="O94" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>26.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
@@ -7518,44 +7518,44 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>1</v>
+        <v>2.42</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O95" s="13" t="n">
-        <v>0</v>
+        <v>224.05</v>
       </c>
       <c r="P95" s="13" t="n">
-        <v>0</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7565,12 +7565,12 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -7590,33 +7590,33 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.25</v>
+        <v>2.42</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="16" t="n">
-        <v>0</v>
+        <v>187.5</v>
+      </c>
+      <c r="O96" s="17" t="n">
+        <v>62.5</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>0</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="97">
@@ -7673,49 +7673,47 @@
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="13" t="n">
-        <v>224.05</v>
+        <v>787.5</v>
+      </c>
+      <c r="O97" s="17" t="n">
+        <v>262.5</v>
       </c>
       <c r="P97" s="13" t="n">
-        <v>92.70999999999999</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="inlineStr">
-        <is>
-          <t>Paramétrages complémentaires + Vision</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v/>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
@@ -7734,64 +7732,64 @@
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>2.42</v>
+        <v>0.5</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O98" s="17" t="n">
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+      <c r="O98" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>25.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -7801,49 +7799,49 @@
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>787.5</v>
+        <v>725</v>
       </c>
       <c r="O99" s="17" t="n">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="P99" s="13" t="n">
-        <v>108.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7853,7 +7851,7 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
+          <t>COMMUNE DE BOBIGNY</t>
         </is>
       </c>
       <c r="E100" s="15" t="n">
@@ -7871,69 +7869,69 @@
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="16" t="n">
-        <v>0</v>
+        <v>1351.26</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>0</v>
+        <v>540.5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -7943,34 +7941,34 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>725</v>
-      </c>
-      <c r="O101" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="13" t="n">
@@ -7980,12 +7978,12 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -7995,11 +7993,13 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
@@ -8018,33 +8018,33 @@
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O102" s="16" t="n">
-        <v>1351.26</v>
+        <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>675.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
@@ -8245,18 +8245,18 @@
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="13" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O105" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="13" t="n">
@@ -8266,12 +8266,12 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8281,13 +8281,11 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v/>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
@@ -8301,28 +8299,28 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>1.35</v>
+        <v>4.25</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8338,12 +8336,12 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -8353,13 +8351,11 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v/>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
@@ -8378,58 +8374,60 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>1.35</v>
+        <v>8.25</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O107" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O107" s="13" t="n">
+        <v>1280</v>
       </c>
       <c r="P107" s="13" t="n">
-        <v>0</v>
+        <v>155.15</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
@@ -8443,28 +8441,28 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>4.25</v>
+        <v>0.25</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8480,22 +8478,22 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>MAIRIE DE PLAN D'ORGON</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
@@ -8518,60 +8516,58 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>8.25</v>
+        <v>3</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O109" s="13" t="n">
-        <v>1280</v>
+        <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
-        <v>155.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v/>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
@@ -8590,29 +8586,29 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O110" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8622,26 +8618,28 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25354</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Duncan HAMELIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE PLAN D'ORGON</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
@@ -8660,23 +8658,23 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26768</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00141775</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
@@ -8692,12 +8690,12 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -8707,11 +8705,13 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
@@ -8720,39 +8720,31 @@
       </c>
       <c r="G112" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L112" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27017</t>
-        </is>
-      </c>
-      <c r="M112" s="15" t="inlineStr">
-        <is>
-          <t>00141205</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L112" s="15" t="inlineStr"/>
+      <c r="M112" s="15" t="inlineStr"/>
       <c r="N112" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O112" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="16" t="n">
@@ -8762,12 +8754,12 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
@@ -8777,13 +8769,11 @@
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E113" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VILLE DE GENNEVILLIERS</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v/>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
@@ -8802,23 +8792,23 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
@@ -8834,28 +8824,26 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>VILLE DE GENNEVILLIERS</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v/>
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
@@ -8864,27 +8852,35 @@
       </c>
       <c r="G114" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L114" s="15" t="inlineStr"/>
-      <c r="M114" s="15" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L114" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27995</t>
+        </is>
+      </c>
+      <c r="M114" s="15" t="inlineStr">
+        <is>
+          <t>501218</t>
+        </is>
+      </c>
       <c r="N114" s="16" t="n">
         <v>0</v>
       </c>
@@ -8898,22 +8894,22 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8936,23 +8932,23 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
@@ -8968,22 +8964,22 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -9006,23 +9002,23 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
@@ -9038,12 +9034,12 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -9053,7 +9049,7 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
@@ -9076,23 +9072,23 @@
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>3</v>
+        <v>1.31</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
@@ -9108,12 +9104,12 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
@@ -9123,7 +9119,7 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9146,23 +9142,23 @@
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.25</v>
+        <v>1.31</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9193,7 +9189,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9227,12 +9223,12 @@
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9297,12 +9293,12 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9318,22 +9314,22 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9351,34 +9347,34 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>1.31</v>
+        <v>0.5</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="13" t="n">
+        <v>401</v>
+      </c>
+      <c r="O121" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="13" t="n">
@@ -9388,12 +9384,12 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
@@ -9403,7 +9399,7 @@
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9419,32 +9415,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H122" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H122" s="15" t="inlineStr"/>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="L122" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27365</t>
-        </is>
-      </c>
-      <c r="M122" s="15" t="inlineStr">
-        <is>
-          <t>491593</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr"/>
+      <c r="M122" s="15" t="inlineStr"/>
       <c r="N122" s="16" t="n">
         <v>0</v>
       </c>
@@ -9458,12 +9442,12 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
@@ -9473,7 +9457,7 @@
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9491,34 +9475,34 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
-        <v>401</v>
-      </c>
-      <c r="O123" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="13" t="n">
@@ -9528,12 +9512,12 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
@@ -9543,7 +9527,7 @@
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9559,10 +9543,14 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H124" s="15" t="inlineStr"/>
+      <c r="H124" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
@@ -9571,8 +9559,16 @@
       <c r="K124" s="15" t="n">
         <v>0.5</v>
       </c>
-      <c r="L124" s="15" t="inlineStr"/>
-      <c r="M124" s="15" t="inlineStr"/>
+      <c r="L124" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M124" s="15" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N124" s="16" t="n">
         <v>0</v>
       </c>
@@ -9586,12 +9582,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9601,7 +9597,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9619,34 +9615,34 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="13" t="n">
+        <v>230</v>
+      </c>
+      <c r="O125" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="13" t="n">
@@ -9656,12 +9652,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9671,7 +9667,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9684,35 +9680,23 @@
       </c>
       <c r="G126" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr"/>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L126" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28035</t>
-        </is>
-      </c>
-      <c r="M126" s="15" t="inlineStr">
-        <is>
-          <t>468660</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L126" s="15" t="inlineStr"/>
+      <c r="M126" s="15" t="inlineStr"/>
       <c r="N126" s="16" t="n">
         <v>0</v>
       </c>
@@ -9726,12 +9710,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9741,7 +9725,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9759,34 +9743,34 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
-        <v>230</v>
-      </c>
-      <c r="O127" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9796,22 +9780,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9824,23 +9808,35 @@
       </c>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H128" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr"/>
-      <c r="M128" s="15" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M128" s="15" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
@@ -9854,22 +9850,22 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9892,23 +9888,23 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
@@ -9924,22 +9920,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9957,28 +9953,28 @@
       </c>
       <c r="H130" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K130" s="15" t="n">
         <v>0.25</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28214</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>458286</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
@@ -9994,22 +9990,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10022,7 +10018,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -10032,25 +10028,17 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L131" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28215</t>
-        </is>
-      </c>
-      <c r="M131" s="12" t="inlineStr">
-        <is>
-          <t>458306</t>
-        </is>
-      </c>
+        <v>6.25</v>
+      </c>
+      <c r="L131" s="12" t="inlineStr"/>
+      <c r="M131" s="12" t="inlineStr"/>
       <c r="N131" s="13" t="n">
         <v>0</v>
       </c>
@@ -10064,22 +10052,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10092,7 +10080,7 @@
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H132" s="15" t="inlineStr">
@@ -10102,25 +10090,17 @@
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28214</t>
-        </is>
-      </c>
-      <c r="M132" s="15" t="inlineStr">
-        <is>
-          <t>458286</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr"/>
+      <c r="M132" s="15" t="inlineStr"/>
       <c r="N132" s="16" t="n">
         <v>0</v>
       </c>
@@ -10134,22 +10114,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10157,36 +10137,44 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L133" s="12" t="inlineStr"/>
-      <c r="M133" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L133" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M133" s="12" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N133" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O133" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="13" t="n">
@@ -10196,12 +10184,12 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
@@ -10211,7 +10199,7 @@
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10224,27 +10212,35 @@
       </c>
       <c r="G134" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L134" s="15" t="inlineStr"/>
-      <c r="M134" s="15" t="inlineStr"/>
+        <v>0.38</v>
+      </c>
+      <c r="L134" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M134" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N134" s="16" t="n">
         <v>0</v>
       </c>
@@ -10258,22 +10254,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10281,7 +10277,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -10291,34 +10287,34 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O135" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P135" s="13" t="n">
@@ -10328,12 +10324,12 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
@@ -10343,7 +10339,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10373,22 +10369,22 @@
         <v>20</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="16" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O136" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="16" t="n">
@@ -10398,22 +10394,22 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10426,7 +10422,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H137" s="12" t="inlineStr">
@@ -10436,25 +10432,17 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L137" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28020</t>
-        </is>
-      </c>
-      <c r="M137" s="12" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr"/>
+      <c r="M137" s="12" t="inlineStr"/>
       <c r="N137" s="13" t="n">
         <v>0</v>
       </c>
@@ -10468,12 +10456,12 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
@@ -10483,7 +10471,7 @@
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10496,7 +10484,7 @@
       </c>
       <c r="G138" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H138" s="15" t="inlineStr">
@@ -10506,29 +10494,29 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28003</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>412981</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O138" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="16" t="n">
@@ -10538,12 +10526,12 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
@@ -10553,7 +10541,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10576,14 +10564,14 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L139" s="12" t="inlineStr"/>
       <c r="M139" s="12" t="inlineStr"/>
@@ -10600,12 +10588,12 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
@@ -10615,7 +10603,7 @@
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10638,25 +10626,17 @@
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L140" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M140" s="15" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L140" s="15" t="inlineStr"/>
+      <c r="M140" s="15" t="inlineStr"/>
       <c r="N140" s="16" t="n">
         <v>0</v>
       </c>
@@ -10670,22 +10650,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10703,19 +10683,19 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L141" s="12" t="inlineStr"/>
       <c r="M141" s="12" t="inlineStr"/>
@@ -10732,12 +10712,12 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
@@ -10747,7 +10727,7 @@
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10760,7 +10740,7 @@
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H142" s="15" t="inlineStr">
@@ -10770,17 +10750,25 @@
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L142" s="15" t="inlineStr"/>
-      <c r="M142" s="15" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L142" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M142" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N142" s="16" t="n">
         <v>0</v>
       </c>
@@ -10794,22 +10782,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10825,21 +10813,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H143" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H143" s="12" t="inlineStr"/>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L143" s="12" t="inlineStr"/>
       <c r="M143" s="12" t="inlineStr"/>
@@ -10856,22 +10840,22 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10884,33 +10868,33 @@
       </c>
       <c r="G144" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27990</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>406296</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N144" s="16" t="n">
@@ -10926,12 +10910,12 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
@@ -10941,7 +10925,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>CD79 - Deux Sèvres</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -10957,17 +10941,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H145" s="12" t="inlineStr"/>
+      <c r="H145" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I145" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J145" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L145" s="12" t="inlineStr"/>
       <c r="M145" s="12" t="inlineStr"/>
@@ -10984,26 +10972,28 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD 14] Paramétrages</t>
         </is>
       </c>
       <c r="C146" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
-        </is>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E146" s="15" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
       </c>
       <c r="F146" s="15" t="inlineStr">
         <is>
@@ -11017,30 +11007,22 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L146" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M146" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr"/>
+      <c r="M146" s="15" t="inlineStr"/>
       <c r="N146" s="16" t="n">
         <v>0</v>
       </c>
@@ -11054,26 +11036,24 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C147" s="12" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr"/>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
-        </is>
-      </c>
-      <c r="E147" s="12" t="n">
-        <v/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
@@ -11092,14 +11072,14 @@
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="L147" s="12" t="inlineStr"/>
       <c r="M147" s="12" t="inlineStr"/>
@@ -11116,27 +11096,27 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E148" s="15" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Montée de version + Pastell</t>
         </is>
       </c>
       <c r="F148" s="15" t="inlineStr">
@@ -11156,14 +11136,14 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr"/>
       <c r="M148" s="15" t="inlineStr"/>
@@ -11180,25 +11160,21 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr"/>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E149" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="E149" s="12" t="inlineStr"/>
       <c r="F149" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11206,24 +11182,20 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H149" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H149" s="12" t="inlineStr"/>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="L149" s="12" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr"/>
@@ -11240,29 +11212,21 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C150" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="inlineStr"/>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
-        </is>
-      </c>
-      <c r="E150" s="15" t="inlineStr">
-        <is>
-          <t>Montée de version + Pastell</t>
-        </is>
-      </c>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="E150" s="15" t="inlineStr"/>
       <c r="F150" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11270,24 +11234,20 @@
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H150" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H150" s="15" t="inlineStr"/>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L150" s="15" t="inlineStr"/>
       <c r="M150" s="15" t="inlineStr"/>
@@ -11304,18 +11264,18 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr"/>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr"/>
@@ -11326,48 +11286,56 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr"/>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K151" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr"/>
-      <c r="M151" s="12" t="inlineStr"/>
+      <c r="L151" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M151" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O151" s="13" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
       <c r="P151" s="13" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr"/>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E152" s="15" t="inlineStr"/>
@@ -11384,11 +11352,11 @@
       <c r="H152" s="15" t="inlineStr"/>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="K152" s="15" t="n">
         <v>0.25</v>
@@ -11408,18 +11376,18 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-583</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Cournonsec</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr"/>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Cournonsec</t>
         </is>
       </c>
       <c r="E153" s="12" t="inlineStr"/>
@@ -11430,171 +11398,59 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H153" s="12" t="inlineStr"/>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>20/03/2025</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L153" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M153" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L153" s="12" t="inlineStr"/>
+      <c r="M153" s="12" t="inlineStr"/>
       <c r="N153" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O153" s="13" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
       <c r="P153" s="13" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="14" t="inlineStr">
-        <is>
-          <t>PSC-850</t>
-        </is>
-      </c>
-      <c r="B154" s="15" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="C154" s="15" t="inlineStr"/>
-      <c r="D154" s="15" t="inlineStr">
-        <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="E154" s="15" t="inlineStr"/>
-      <c r="F154" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G154" s="15" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H154" s="15" t="inlineStr"/>
-      <c r="I154" s="15" t="inlineStr">
-        <is>
-          <t>10/06/2025</t>
-        </is>
-      </c>
-      <c r="J154" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="K154" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L154" s="15" t="inlineStr"/>
-      <c r="M154" s="15" t="inlineStr"/>
-      <c r="N154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O154" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P154" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="11" t="inlineStr">
-        <is>
-          <t>PSC-583</t>
-        </is>
-      </c>
-      <c r="B155" s="12" t="inlineStr">
-        <is>
-          <t>Cournonsec</t>
-        </is>
-      </c>
-      <c r="C155" s="12" t="inlineStr"/>
-      <c r="D155" s="12" t="inlineStr">
-        <is>
-          <t>Cournonsec</t>
-        </is>
-      </c>
-      <c r="E155" s="12" t="inlineStr"/>
-      <c r="F155" s="12" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G155" s="12" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H155" s="12" t="inlineStr"/>
-      <c r="I155" s="12" t="inlineStr">
-        <is>
-          <t>20/03/2025</t>
-        </is>
-      </c>
-      <c r="J155" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K155" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L155" s="12" t="inlineStr"/>
-      <c r="M155" s="12" t="inlineStr"/>
-      <c r="N155" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O155" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P155" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="18" t="inlineStr">
+      <c r="A154" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B156" s="18" t="inlineStr"/>
-      <c r="C156" s="18" t="inlineStr"/>
-      <c r="D156" s="18" t="inlineStr"/>
-      <c r="E156" s="18" t="inlineStr"/>
-      <c r="F156" s="18" t="inlineStr"/>
-      <c r="G156" s="18" t="inlineStr"/>
-      <c r="H156" s="18" t="inlineStr"/>
-      <c r="I156" s="18" t="inlineStr"/>
-      <c r="J156" s="18" t="inlineStr"/>
-      <c r="K156" s="18" t="inlineStr"/>
-      <c r="L156" s="18" t="inlineStr"/>
-      <c r="M156" s="18" t="inlineStr"/>
-      <c r="N156" s="19" t="n">
-        <v>63800.794</v>
-      </c>
-      <c r="O156" s="19" t="n">
-        <v>30317.837</v>
-      </c>
-      <c r="P156" s="19" t="n">
-        <v>130.81</v>
+      <c r="B154" s="18" t="inlineStr"/>
+      <c r="C154" s="18" t="inlineStr"/>
+      <c r="D154" s="18" t="inlineStr"/>
+      <c r="E154" s="18" t="inlineStr"/>
+      <c r="F154" s="18" t="inlineStr"/>
+      <c r="G154" s="18" t="inlineStr"/>
+      <c r="H154" s="18" t="inlineStr"/>
+      <c r="I154" s="18" t="inlineStr"/>
+      <c r="J154" s="18" t="inlineStr"/>
+      <c r="K154" s="18" t="inlineStr"/>
+      <c r="L154" s="18" t="inlineStr"/>
+      <c r="M154" s="18" t="inlineStr"/>
+      <c r="N154" s="19" t="n">
+        <v>58002.895</v>
+      </c>
+      <c r="O154" s="19" t="n">
+        <v>30640.187</v>
+      </c>
+      <c r="P154" s="19" t="n">
+        <v>129.55</v>
       </c>
     </row>
   </sheetData>
@@ -11749,8 +11605,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId151"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12454,26 +12308,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>171</v>
+        <v>174.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>32.25</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>12.75</v>
+        <v>13.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>216</v>
+        <v>220.75</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>69.75</v>
+        <v>75.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>532.88</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.4%</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12369,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>189.75</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -12600,10 +12454,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>369856</v>
+        <v>369534</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>138048</v>
+        <v>137726</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>231808</v>
@@ -12625,10 +12479,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>166211</v>
+        <v>165889</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>62111</v>
+        <v>61788</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>104101</v>

--- a/jira_export_2026-08-27.xlsx
+++ b/jira_export_2026-08-27.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>30,640 €</t>
+          <t>32,101 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>16,647 €</t>
+          <t>18,108 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>516 h</t>
+          <t>522 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P154"/>
+  <dimension ref="A1:P153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3682,32 +3682,32 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -3717,49 +3717,49 @@
       </c>
       <c r="H42" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J42" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K42" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M42" s="15" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N42" s="16" t="n">
-        <v>680</v>
-      </c>
-      <c r="O42" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>787.5</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0</v>
+        <v>393.75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -3801,37 +3801,37 @@
         <v>2</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N43" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>787.5</v>
+        <v>438.2</v>
       </c>
       <c r="P43" s="13" t="n">
-        <v>393.75</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
@@ -3873,52 +3873,52 @@
         <v>2</v>
       </c>
       <c r="K44" s="15" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="L44" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M44" s="15" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N44" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="16" t="n">
-        <v>438.2</v>
+        <v>1890</v>
+      </c>
+      <c r="O44" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>46.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -3938,44 +3938,44 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J45" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M45" s="12" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N45" s="13" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O45" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>66.55</v>
       </c>
       <c r="P45" s="13" t="n">
-        <v>0</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
@@ -4010,64 +4010,64 @@
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J46" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K46" s="15" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M46" s="15" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N46" s="16" t="n">
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="O46" s="16" t="n">
-        <v>66.55</v>
+        <v>966</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>133.1</v>
+        <v>483</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B47" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -4077,49 +4077,49 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J47" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N47" s="13" t="n">
-        <v>920</v>
-      </c>
-      <c r="O47" s="13" t="n">
-        <v>966</v>
+        <v>3602.4</v>
+      </c>
+      <c r="O47" s="17" t="n">
+        <v>821.6</v>
       </c>
       <c r="P47" s="13" t="n">
-        <v>483</v>
+        <v>821.6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33638</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
@@ -4129,12 +4129,12 @@
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOULINS</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier et MEP module Caisse</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
@@ -4154,59 +4154,59 @@
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J48" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K48" s="15" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33647</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M48" s="15" t="inlineStr">
         <is>
-          <t>00169251</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N48" s="16" t="n">
-        <v>3602.4</v>
+        <v>4040</v>
       </c>
       <c r="O48" s="17" t="n">
-        <v>821.6</v>
+        <v>3535</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>821.6</v>
+        <v>1571.11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
@@ -4233,57 +4233,57 @@
         <v>2</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N49" s="13" t="n">
-        <v>4040</v>
-      </c>
-      <c r="O49" s="17" t="n">
-        <v>3535</v>
+        <v>0</v>
+      </c>
+      <c r="O49" s="13" t="n">
+        <v>691.9</v>
       </c>
       <c r="P49" s="13" t="n">
-        <v>1571.11</v>
+        <v>691.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
@@ -4298,44 +4298,44 @@
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J50" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M50" s="15" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N50" s="16" t="n">
-        <v>1017.5</v>
+        <v>171.4</v>
       </c>
       <c r="O50" s="17" t="n">
-        <v>691.9</v>
+        <v>0</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>691.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B51" s="12" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J51" s="12" t="n">
@@ -4381,19 +4381,19 @@
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M51" s="12" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N51" s="13" t="n">
-        <v>1416</v>
-      </c>
-      <c r="O51" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>1460.9</v>
       </c>
       <c r="P51" s="13" t="n">
         <v>0</v>
@@ -4402,32 +4402,32 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="I52" s="15" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J52" s="15" t="n">
@@ -4453,16 +4453,16 @@
       </c>
       <c r="L52" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M52" s="15" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N52" s="16" t="n">
-        <v>171.4</v>
+        <v>344</v>
       </c>
       <c r="O52" s="17" t="n">
         <v>0</v>
@@ -4474,32 +4474,32 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -4521,37 +4521,37 @@
         <v>3</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M53" s="12" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N53" s="13" t="n">
-        <v>344</v>
-      </c>
-      <c r="O53" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>642.75</v>
       </c>
       <c r="P53" s="13" t="n">
-        <v>0</v>
+        <v>514.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -4586,64 +4586,64 @@
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J54" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K54" s="15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M54" s="15" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N54" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O54" s="16" t="n">
-        <v>642.75</v>
+        <v>224.76</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>514.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J55" s="12" t="n">
@@ -4669,19 +4669,19 @@
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33315</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M55" s="12" t="inlineStr">
         <is>
-          <t>00167138</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N55" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="13" t="n">
-        <v>224.76</v>
+        <v>500</v>
+      </c>
+      <c r="O55" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P55" s="13" t="n">
         <v>0</v>
@@ -4690,27 +4690,27 @@
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J56" s="15" t="n">
@@ -4741,16 +4741,16 @@
       </c>
       <c r="L56" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M56" s="15" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N56" s="16" t="n">
-        <v>500</v>
+        <v>149</v>
       </c>
       <c r="O56" s="17" t="n">
         <v>0</v>
@@ -4762,32 +4762,32 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B57" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -4797,38 +4797,38 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J57" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>0</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L57" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M57" s="12" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N57" s="13" t="n">
-        <v>149</v>
-      </c>
-      <c r="O57" s="17" t="n">
-        <v>0</v>
+        <v>625</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>652.5</v>
       </c>
       <c r="P57" s="13" t="n">
-        <v>0</v>
+        <v>75.65000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -4881,57 +4881,57 @@
         <v>3</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>8.380000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M58" s="15" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N58" s="16" t="n">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>652.5</v>
+        <v>192</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>77.91</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B59" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -4941,49 +4941,49 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J59" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>8.380000000000001</v>
+        <v>5</v>
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M59" s="12" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N59" s="13" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>192</v>
+        <v>910</v>
       </c>
       <c r="P59" s="13" t="n">
-        <v>22.93</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5018,59 +5018,59 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M60" s="15" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N60" s="16" t="n">
-        <v>910</v>
-      </c>
-      <c r="O60" s="16" t="n">
-        <v>910</v>
+        <v>1207</v>
+      </c>
+      <c r="O60" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -5090,64 +5090,64 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J61" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M61" s="12" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N61" s="13" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O61" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>323.7</v>
       </c>
       <c r="P61" s="13" t="n">
-        <v>0</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
@@ -5157,69 +5157,69 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J62" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K62" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L62" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M62" s="15" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N62" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="16" t="n">
-        <v>323.7</v>
+        <v>500</v>
+      </c>
+      <c r="O62" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>1294.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="12" t="inlineStr">
@@ -5241,22 +5241,22 @@
         <v>4</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M63" s="12" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N63" s="13" t="n">
-        <v>500</v>
-      </c>
-      <c r="O63" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="13" t="n">
@@ -5266,12 +5266,12 @@
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32950</t>
         </is>
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Migration GeODP Placier 1/2</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
@@ -5313,23 +5313,23 @@
         <v>4</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32958</t>
         </is>
       </c>
       <c r="M64" s="15" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165249</t>
         </is>
       </c>
       <c r="N64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O64" s="16" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="P64" s="16" t="n">
         <v>0</v>
@@ -5338,32 +5338,32 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32950</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 1/2</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -5373,35 +5373,35 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J65" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L65" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32958</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M65" s="12" t="inlineStr">
         <is>
-          <t>00165249</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N65" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="P65" s="13" t="n">
         <v>0</v>
@@ -5410,12 +5410,12 @@
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
@@ -5450,44 +5450,44 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J66" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0.25</v>
+        <v>2.75</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M66" s="15" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O66" s="16" t="n">
-        <v>0</v>
+        <v>219.36</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H67" s="12" t="inlineStr">
@@ -5522,44 +5522,36 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J67" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L67" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-32629</t>
-        </is>
-      </c>
-      <c r="M67" s="12" t="inlineStr">
-        <is>
-          <t>00163182</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L67" s="12" t="inlineStr"/>
+      <c r="M67" s="12" t="inlineStr"/>
       <c r="N67" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>219.36</v>
+        <v>0</v>
       </c>
       <c r="P67" s="13" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
@@ -5569,12 +5561,12 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
@@ -5584,7 +5576,7 @@
       </c>
       <c r="G68" s="15" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
@@ -5601,14 +5593,22 @@
         <v>4</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="L68" s="15" t="inlineStr"/>
-      <c r="M68" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32556</t>
+        </is>
+      </c>
+      <c r="M68" s="15" t="inlineStr">
+        <is>
+          <t>00162313</t>
+        </is>
+      </c>
       <c r="N68" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="16" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O68" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="16" t="n">
@@ -5618,32 +5618,32 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -5653,32 +5653,32 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J69" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M69" s="12" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N69" s="13" t="n">
-        <v>142.1</v>
+        <v>2335</v>
       </c>
       <c r="O69" s="17" t="n">
         <v>0</v>
@@ -5690,32 +5690,32 @@
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="15" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G70" s="15" t="inlineStr">
@@ -5725,34 +5725,34 @@
       </c>
       <c r="H70" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J70" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K70" s="15" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L70" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M70" s="15" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N70" s="16" t="n">
-        <v>2335</v>
-      </c>
-      <c r="O70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="16" t="n">
@@ -5762,32 +5762,32 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B71" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -5797,34 +5797,34 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J71" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L71" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M71" s="12" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N71" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="13" t="n">
+        <v>450</v>
+      </c>
+      <c r="O71" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="13" t="n">
@@ -5834,32 +5834,32 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -5869,69 +5869,65 @@
       </c>
       <c r="H72" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>450</v>
+        <v>910</v>
       </c>
       <c r="O72" s="17" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr"/>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -5941,60 +5937,64 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J73" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>910</v>
+        <v>255</v>
       </c>
       <c r="O73" s="17" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>72.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C74" s="15" t="inlineStr"/>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+        </is>
+      </c>
+      <c r="C74" s="15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
@@ -6021,52 +6021,52 @@
         <v>5</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>255</v>
-      </c>
-      <c r="O74" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>100</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -6081,69 +6081,69 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="13" t="n">
-        <v>100</v>
+        <v>590.15</v>
+      </c>
+      <c r="O75" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
@@ -6158,64 +6158,64 @@
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K76" s="15" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O76" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O76" s="16" t="n">
+        <v>109.972</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -6225,69 +6225,69 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>12.75</v>
+        <v>0</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O77" s="13" t="n">
-        <v>109.972</v>
+        <v>285</v>
+      </c>
+      <c r="O77" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>8.630000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J78" s="15" t="n">
@@ -6313,16 +6313,16 @@
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>285</v>
+        <v>1325</v>
       </c>
       <c r="O78" s="17" t="n">
         <v>0</v>
@@ -6334,12 +6334,12 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -6374,7 +6374,7 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
@@ -6385,16 +6385,16 @@
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>1325</v>
+        <v>120</v>
       </c>
       <c r="O79" s="17" t="n">
         <v>0</v>
@@ -6406,32 +6406,32 @@
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
@@ -6457,16 +6457,16 @@
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>120</v>
+        <v>588</v>
       </c>
       <c r="O80" s="17" t="n">
         <v>0</v>
@@ -6478,27 +6478,27 @@
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -6513,32 +6513,32 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>588</v>
+        <v>203.5</v>
       </c>
       <c r="O81" s="17" t="n">
         <v>0</v>
@@ -6550,12 +6550,12 @@
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -6565,12 +6565,12 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H82" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
@@ -6601,16 +6601,16 @@
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
-        <v>203.5</v>
+        <v>300</v>
       </c>
       <c r="O82" s="17" t="n">
         <v>0</v>
@@ -6622,32 +6622,32 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6657,49 +6657,49 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0</v>
+        <v>15.25</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="O83" s="17" t="n">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="O83" s="13" t="n">
+        <v>1934.1</v>
       </c>
       <c r="P83" s="13" t="n">
-        <v>0</v>
+        <v>126.83</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G84" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H84" s="15" t="inlineStr">
@@ -6741,52 +6741,44 @@
         <v>6</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="L84" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31546</t>
-        </is>
-      </c>
-      <c r="M84" s="15" t="inlineStr">
-        <is>
-          <t>00157816</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L84" s="15" t="inlineStr"/>
+      <c r="M84" s="15" t="inlineStr"/>
       <c r="N84" s="16" t="n">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="O84" s="16" t="n">
-        <v>1934.1</v>
+        <v>0</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>126.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -6796,7 +6788,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -6806,56 +6798,64 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L85" s="12" t="inlineStr"/>
-      <c r="M85" s="12" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="L85" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31468</t>
+        </is>
+      </c>
+      <c r="M85" s="12" t="inlineStr">
+        <is>
+          <t>00157346</t>
+        </is>
+      </c>
       <c r="N85" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O85" s="13" t="n">
-        <v>0</v>
+        <v>138.825</v>
       </c>
       <c r="P85" s="13" t="n">
-        <v>0</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -6865,49 +6865,49 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="16" t="n">
-        <v>138.825</v>
+        <v>210</v>
+      </c>
+      <c r="O86" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>19.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
@@ -6953,16 +6953,16 @@
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O87" s="17" t="n">
         <v>0</v>
@@ -6974,12 +6974,12 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -6989,12 +6989,12 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
@@ -7025,16 +7025,16 @@
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O88" s="17" t="n">
         <v>0</v>
@@ -7046,12 +7046,12 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -7086,29 +7086,29 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>255</v>
-      </c>
-      <c r="O89" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="13" t="n">
@@ -7118,12 +7118,12 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7158,29 +7158,29 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>140</v>
+      </c>
+      <c r="O90" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="16" t="n">
@@ -7190,32 +7190,32 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -7225,64 +7225,64 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>140</v>
+        <v>690</v>
       </c>
       <c r="O91" s="17" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="P91" s="13" t="n">
-        <v>0</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="G92" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H92" s="15" t="inlineStr">
@@ -7302,44 +7302,44 @@
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J92" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K92" s="15" t="n">
-        <v>8.75</v>
+        <v>1</v>
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>690</v>
-      </c>
-      <c r="O92" s="17" t="n">
-        <v>230</v>
+        <v>0</v>
+      </c>
+      <c r="O92" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P92" s="16" t="n">
-        <v>26.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -7374,23 +7374,23 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J93" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
@@ -7406,12 +7406,12 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7446,33 +7446,33 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>7</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0.25</v>
+        <v>2.42</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="16" t="n">
-        <v>0</v>
+        <v>224.05</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>0</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -7529,22 +7529,22 @@
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" s="13" t="n">
-        <v>224.05</v>
+        <v>187.5</v>
+      </c>
+      <c r="O95" s="17" t="n">
+        <v>62.5</v>
       </c>
       <c r="P95" s="13" t="n">
-        <v>92.70999999999999</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="96">
@@ -7601,49 +7601,47 @@
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>187.5</v>
+        <v>787.5</v>
       </c>
       <c r="O96" s="17" t="n">
-        <v>62.5</v>
+        <v>262.5</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>25.86</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="inlineStr">
-        <is>
-          <t>Paramétrages complémentaires + Vision</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v/>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
@@ -7662,62 +7660,64 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>2.42</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>787.5</v>
-      </c>
-      <c r="O97" s="17" t="n">
-        <v>262.5</v>
+        <v>0</v>
+      </c>
+      <c r="O97" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="P97" s="13" t="n">
-        <v>108.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G98" s="15" t="inlineStr">
@@ -7727,34 +7727,34 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J98" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="16" t="n">
+        <v>725</v>
+      </c>
+      <c r="O98" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
@@ -7764,32 +7764,30 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v/>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -7799,49 +7797,49 @@
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>725</v>
-      </c>
-      <c r="O99" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O99" s="13" t="n">
+        <v>1351.26</v>
       </c>
       <c r="P99" s="13" t="n">
-        <v>0</v>
+        <v>450.42</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
@@ -7851,11 +7849,13 @@
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
@@ -7874,33 +7874,33 @@
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="16" t="n">
-        <v>1351.26</v>
+        <v>0</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>540.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -7953,16 +7953,16 @@
         <v>9</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
@@ -8025,16 +8025,16 @@
         <v>9</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
@@ -8097,16 +8097,16 @@
         <v>9</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
@@ -8169,22 +8169,22 @@
         <v>9</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O104" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
@@ -8194,12 +8194,12 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -8209,13 +8209,11 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v/>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
@@ -8229,34 +8227,34 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>1.35</v>
+        <v>4.25</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O105" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="13" t="n">
@@ -8266,12 +8264,12 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8281,7 +8279,7 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E106" s="15" t="n">
@@ -8299,63 +8297,65 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>4.25</v>
+        <v>8.25</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O106" s="16" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>0</v>
+        <v>155.15</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
@@ -8374,60 +8374,58 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>8.25</v>
+        <v>0.25</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O107" s="13" t="n">
-        <v>1280</v>
+        <v>0</v>
       </c>
       <c r="P107" s="13" t="n">
-        <v>155.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E108" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>MAIRIE DE PLAN D'ORGON</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v/>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
@@ -8446,23 +8444,23 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8478,22 +8476,22 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-25354</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Duncan HAMELIN</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE PLAN D'ORGON</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
@@ -8516,29 +8514,29 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26768</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00141775</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O109" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
@@ -8548,26 +8546,28 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
@@ -8586,29 +8586,29 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O110" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8618,27 +8618,27 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Script purge de données</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -8648,35 +8648,27 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L111" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27578</t>
-        </is>
-      </c>
-      <c r="M111" s="12" t="inlineStr">
-        <is>
-          <t>499043</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L111" s="12" t="inlineStr"/>
+      <c r="M111" s="12" t="inlineStr"/>
       <c r="N111" s="13" t="n">
         <v>0</v>
       </c>
@@ -8690,28 +8682,26 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>VILLE DE GENNEVILLIERS</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v/>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
@@ -8720,27 +8710,35 @@
       </c>
       <c r="G112" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>11</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L112" s="15" t="inlineStr"/>
-      <c r="M112" s="15" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L112" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27996</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="inlineStr">
+        <is>
+          <t>501219</t>
+        </is>
+      </c>
       <c r="N112" s="16" t="n">
         <v>0</v>
       </c>
@@ -8803,12 +8801,12 @@
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
@@ -8824,22 +8822,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8862,23 +8860,23 @@
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
@@ -8894,12 +8892,12 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
@@ -8909,7 +8907,7 @@
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8932,23 +8930,23 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
@@ -8964,12 +8962,12 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
@@ -8979,7 +8977,7 @@
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -9002,23 +9000,23 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>13</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.25</v>
+        <v>1.31</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
@@ -9083,12 +9081,12 @@
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
@@ -9119,7 +9117,7 @@
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9153,12 +9151,12 @@
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9189,7 +9187,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9223,12 +9221,12 @@
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9244,22 +9242,22 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9277,34 +9275,34 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>1.31</v>
+        <v>0.5</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="16" t="n">
+        <v>401</v>
+      </c>
+      <c r="O120" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="16" t="n">
@@ -9314,22 +9312,22 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9345,36 +9343,24 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H121" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H121" s="12" t="inlineStr"/>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K121" s="12" t="n">
         <v>0.5</v>
       </c>
-      <c r="L121" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27373</t>
-        </is>
-      </c>
-      <c r="M121" s="12" t="inlineStr">
-        <is>
-          <t>466234</t>
-        </is>
-      </c>
+      <c r="L121" s="12" t="inlineStr"/>
+      <c r="M121" s="12" t="inlineStr"/>
       <c r="N121" s="13" t="n">
-        <v>401</v>
-      </c>
-      <c r="O121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="13" t="n">
@@ -9384,22 +9370,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9415,7 +9401,11 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H122" s="15" t="inlineStr"/>
+      <c r="H122" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -9425,10 +9415,18 @@
         <v>16</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L122" s="15" t="inlineStr"/>
-      <c r="M122" s="15" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M122" s="15" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N122" s="16" t="n">
         <v>0</v>
       </c>
@@ -9442,22 +9440,22 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9475,28 +9473,28 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9512,22 +9510,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9550,29 +9548,29 @@
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="16" t="n">
+        <v>230</v>
+      </c>
+      <c r="O124" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="16" t="n">
@@ -9582,22 +9580,22 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9610,39 +9608,27 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H125" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr"/>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28034</t>
-        </is>
-      </c>
-      <c r="M125" s="12" t="inlineStr">
-        <is>
-          <t>475575</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L125" s="12" t="inlineStr"/>
+      <c r="M125" s="12" t="inlineStr"/>
       <c r="N125" s="13" t="n">
-        <v>230</v>
-      </c>
-      <c r="O125" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="13" t="n">
@@ -9652,22 +9638,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9680,23 +9666,35 @@
       </c>
       <c r="G126" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H126" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L126" s="15" t="inlineStr"/>
-      <c r="M126" s="15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L126" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M126" s="15" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N126" s="16" t="n">
         <v>0</v>
       </c>
@@ -9710,12 +9708,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9725,7 +9723,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9743,28 +9741,28 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
@@ -9780,22 +9778,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9813,28 +9811,28 @@
       </c>
       <c r="H128" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L128" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N128" s="16" t="n">
@@ -9895,16 +9893,16 @@
         <v>18</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28215</t>
+          <t>PDMDEP-28214</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>458286</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
@@ -9920,22 +9918,22 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19558</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>VILLEFONTAINE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9948,7 +9946,7 @@
       </c>
       <c r="G130" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H130" s="15" t="inlineStr">
@@ -9958,25 +9956,17 @@
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>28/02/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L130" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28214</t>
-        </is>
-      </c>
-      <c r="M130" s="15" t="inlineStr">
-        <is>
-          <t>458286</t>
-        </is>
-      </c>
+        <v>6.25</v>
+      </c>
+      <c r="L130" s="15" t="inlineStr"/>
+      <c r="M130" s="15" t="inlineStr"/>
       <c r="N130" s="16" t="n">
         <v>0</v>
       </c>
@@ -9990,12 +9980,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -10005,7 +9995,7 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10028,14 +10018,14 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>6.25</v>
+        <v>1.5</v>
       </c>
       <c r="L131" s="12" t="inlineStr"/>
       <c r="M131" s="12" t="inlineStr"/>
@@ -10052,22 +10042,22 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10075,36 +10065,44 @@
       </c>
       <c r="F132" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>20</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr"/>
-      <c r="M132" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M132" s="15" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N132" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O132" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P132" s="16" t="n">
@@ -10114,22 +10112,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10137,7 +10135,7 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -10147,34 +10145,34 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>20</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O133" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="13" t="n">
@@ -10199,7 +10197,7 @@
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10233,7 +10231,7 @@
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
@@ -10254,12 +10252,12 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
@@ -10269,7 +10267,7 @@
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10299,22 +10297,22 @@
         <v>20</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28023</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>454387</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" s="13" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O135" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P135" s="13" t="n">
@@ -10324,22 +10322,22 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10352,7 +10350,7 @@
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr">
@@ -10362,29 +10360,21 @@
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M136" s="15" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr"/>
+      <c r="M136" s="15" t="inlineStr"/>
       <c r="N136" s="16" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P136" s="16" t="n">
@@ -10394,22 +10384,22 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10432,17 +10422,25 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L137" s="12" t="inlineStr"/>
-      <c r="M137" s="12" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N137" s="13" t="n">
         <v>0</v>
       </c>
@@ -10456,22 +10454,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10494,25 +10492,17 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L138" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M138" s="15" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L138" s="15" t="inlineStr"/>
+      <c r="M138" s="15" t="inlineStr"/>
       <c r="N138" s="16" t="n">
         <v>0</v>
       </c>
@@ -10526,22 +10516,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10564,14 +10554,14 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L139" s="12" t="inlineStr"/>
       <c r="M139" s="12" t="inlineStr"/>
@@ -10588,12 +10578,12 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
@@ -10603,7 +10593,7 @@
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10621,19 +10611,19 @@
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
         <v>33</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L140" s="15" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -10650,12 +10640,12 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
@@ -10665,7 +10655,7 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10678,27 +10668,35 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L141" s="12" t="inlineStr"/>
-      <c r="M141" s="12" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
@@ -10712,22 +10710,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10740,35 +10738,23 @@
       </c>
       <c r="G142" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H142" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H142" s="15" t="inlineStr"/>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L142" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M142" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L142" s="15" t="inlineStr"/>
+      <c r="M142" s="15" t="inlineStr"/>
       <c r="N142" s="16" t="n">
         <v>0</v>
       </c>
@@ -10782,12 +10768,12 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
@@ -10797,7 +10783,7 @@
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10813,20 +10799,32 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H143" s="12" t="inlineStr"/>
+      <c r="H143" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>35</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L143" s="12" t="inlineStr"/>
-      <c r="M143" s="12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N143" s="13" t="n">
         <v>0</v>
       </c>
@@ -10840,12 +10838,12 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
@@ -10855,7 +10853,7 @@
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD79 - Deux Sèvres</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10878,25 +10876,17 @@
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L144" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M144" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L144" s="15" t="inlineStr"/>
+      <c r="M144" s="15" t="inlineStr"/>
       <c r="N144" s="16" t="n">
         <v>0</v>
       </c>
@@ -10910,26 +10900,28 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[CD 14] Paramétrages</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
-        </is>
-      </c>
-      <c r="E145" s="12" t="n">
-        <v/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
@@ -10943,7 +10935,7 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I145" s="12" t="inlineStr">
@@ -10955,7 +10947,7 @@
         <v>35</v>
       </c>
       <c r="K145" s="12" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="L145" s="12" t="inlineStr"/>
       <c r="M145" s="12" t="inlineStr"/>
@@ -10972,27 +10964,23 @@
     <row r="146">
       <c r="A146" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B146" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
-        </is>
-      </c>
-      <c r="C146" s="15" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C146" s="15" t="inlineStr"/>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E146" s="15" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F146" s="15" t="inlineStr">
@@ -11007,19 +10995,19 @@
       </c>
       <c r="H146" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I146" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J146" s="15" t="n">
         <v>35</v>
       </c>
       <c r="K146" s="15" t="n">
-        <v>1.25</v>
+        <v>9</v>
       </c>
       <c r="L146" s="15" t="inlineStr"/>
       <c r="M146" s="15" t="inlineStr"/>
@@ -11036,23 +11024,27 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C147" s="12" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Montée de version + Pastell</t>
         </is>
       </c>
       <c r="F147" s="12" t="inlineStr">
@@ -11067,19 +11059,19 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="L147" s="12" t="inlineStr"/>
       <c r="M147" s="12" t="inlineStr"/>
@@ -11096,29 +11088,21 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C148" s="15" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="C148" s="15" t="inlineStr"/>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
-        </is>
-      </c>
-      <c r="E148" s="15" t="inlineStr">
-        <is>
-          <t>Montée de version + Pastell</t>
-        </is>
-      </c>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="E148" s="15" t="inlineStr"/>
       <c r="F148" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -11126,21 +11110,17 @@
       </c>
       <c r="G148" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H148" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="inlineStr"/>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K148" s="15" t="n">
         <v>0.5</v>
@@ -11160,18 +11140,18 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr"/>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E149" s="12" t="inlineStr"/>
@@ -11188,14 +11168,14 @@
       <c r="H149" s="12" t="inlineStr"/>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L149" s="12" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr"/>
@@ -11212,18 +11192,18 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr"/>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E150" s="15" t="inlineStr"/>
@@ -11234,48 +11214,56 @@
       </c>
       <c r="G150" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H150" s="15" t="inlineStr"/>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K150" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L150" s="15" t="inlineStr"/>
-      <c r="M150" s="15" t="inlineStr"/>
+      <c r="L150" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M150" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O150" s="16" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
       <c r="P150" s="16" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr"/>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E151" s="12" t="inlineStr"/>
@@ -11286,56 +11274,48 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H151" s="12" t="inlineStr"/>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L151" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L151" s="12" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr"/>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O151" s="13" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
       <c r="P151" s="13" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-583</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Cournonsec</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr"/>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>Cournonsec</t>
         </is>
       </c>
       <c r="E152" s="15" t="inlineStr"/>
@@ -11352,11 +11332,11 @@
       <c r="H152" s="15" t="inlineStr"/>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>20/03/2025</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K152" s="15" t="n">
         <v>0.25</v>
@@ -11374,83 +11354,31 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="11" t="inlineStr">
-        <is>
-          <t>PSC-583</t>
-        </is>
-      </c>
-      <c r="B153" s="12" t="inlineStr">
-        <is>
-          <t>Cournonsec</t>
-        </is>
-      </c>
-      <c r="C153" s="12" t="inlineStr"/>
-      <c r="D153" s="12" t="inlineStr">
-        <is>
-          <t>Cournonsec</t>
-        </is>
-      </c>
-      <c r="E153" s="12" t="inlineStr"/>
-      <c r="F153" s="12" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G153" s="12" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H153" s="12" t="inlineStr"/>
-      <c r="I153" s="12" t="inlineStr">
-        <is>
-          <t>20/03/2025</t>
-        </is>
-      </c>
-      <c r="J153" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K153" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L153" s="12" t="inlineStr"/>
-      <c r="M153" s="12" t="inlineStr"/>
-      <c r="N153" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="18" t="inlineStr">
+      <c r="A153" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B154" s="18" t="inlineStr"/>
-      <c r="C154" s="18" t="inlineStr"/>
-      <c r="D154" s="18" t="inlineStr"/>
-      <c r="E154" s="18" t="inlineStr"/>
-      <c r="F154" s="18" t="inlineStr"/>
-      <c r="G154" s="18" t="inlineStr"/>
-      <c r="H154" s="18" t="inlineStr"/>
-      <c r="I154" s="18" t="inlineStr"/>
-      <c r="J154" s="18" t="inlineStr"/>
-      <c r="K154" s="18" t="inlineStr"/>
-      <c r="L154" s="18" t="inlineStr"/>
-      <c r="M154" s="18" t="inlineStr"/>
-      <c r="N154" s="19" t="n">
-        <v>58002.895</v>
-      </c>
-      <c r="O154" s="19" t="n">
-        <v>30640.187</v>
-      </c>
-      <c r="P154" s="19" t="n">
-        <v>129.55</v>
+      <c r="B153" s="18" t="inlineStr"/>
+      <c r="C153" s="18" t="inlineStr"/>
+      <c r="D153" s="18" t="inlineStr"/>
+      <c r="E153" s="18" t="inlineStr"/>
+      <c r="F153" s="18" t="inlineStr"/>
+      <c r="G153" s="18" t="inlineStr"/>
+      <c r="H153" s="18" t="inlineStr"/>
+      <c r="I153" s="18" t="inlineStr"/>
+      <c r="J153" s="18" t="inlineStr"/>
+      <c r="K153" s="18" t="inlineStr"/>
+      <c r="L153" s="18" t="inlineStr"/>
+      <c r="M153" s="18" t="inlineStr"/>
+      <c r="N153" s="19" t="n">
+        <v>54889.395</v>
+      </c>
+      <c r="O153" s="19" t="n">
+        <v>32101.087</v>
+      </c>
+      <c r="P153" s="19" t="n">
+        <v>134.31</v>
       </c>
     </row>
   </sheetData>
@@ -11604,7 +11532,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12308,26 +12235,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>174.75</v>
+        <v>176.75</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>32.25</v>
+        <v>32.75</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>13.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>220.75</v>
+        <v>223.25</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>75.75</v>
+        <v>76.25</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>532.88</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.9%</t>
         </is>
       </c>
     </row>
@@ -12369,7 +12296,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -12454,13 +12381,13 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>369534</v>
+        <v>368073</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>137726</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>231808</v>
+        <v>230347</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>146867</v>
@@ -12469,7 +12396,7 @@
         <v>21179</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>26236</v>
+        <v>24775</v>
       </c>
     </row>
     <row r="6">
@@ -12504,13 +12431,13 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>203645</v>
+        <v>202184</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>75937</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>127708</v>
+        <v>126247</v>
       </c>
       <c r="E7" s="27" t="n">
         <v>59957</v>
@@ -12519,7 +12446,7 @@
         <v>9871</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>22953</v>
+        <v>21492</v>
       </c>
     </row>
   </sheetData>
